--- a/Config/Excel/Tables/怪物表.xlsx
+++ b/Config/Excel/Tables/怪物表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11655"/>
+    <workbookView windowWidth="28560" windowHeight="4650"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -79,6 +79,9 @@
     <t>IsBoss</t>
   </si>
   <si>
+    <t>Prefab</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
     <t>是否是boss</t>
   </si>
   <si>
+    <t>模型预制体</t>
+  </si>
+  <si>
     <t>史莱姆</t>
   </si>
   <si>
@@ -152,6 +158,9 @@
   </si>
   <si>
     <t>101|102</t>
+  </si>
+  <si>
+    <t>Spitter</t>
   </si>
   <si>
     <t>史莱姆王</t>
@@ -173,7 +182,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,6 +192,12 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -659,137 +674,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -797,6 +812,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1108,7 +1124,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="12" max="12" width="12.125" customWidth="1"/>
@@ -1118,7 +1134,7 @@
     <col min="17" max="17" width="11.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:17">
+    <row r="1" ht="14.25" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1168,123 +1184,132 @@
       <c r="Q1" t="s">
         <v>15</v>
       </c>
+      <c r="R1" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" ht="14.25" spans="1:17">
+    <row r="2" ht="14.25" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="3" ht="14.25" spans="1:17">
+    <row r="3" ht="14.25" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q3" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" ht="14.25" spans="1:18">
       <c r="B4">
         <v>200001</v>
       </c>
       <c r="C4">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1308,7 +1333,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -1319,19 +1344,22 @@
       <c r="Q4" t="b">
         <v>0</v>
       </c>
+      <c r="R4" s="3" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" ht="14.25" spans="1:18">
       <c r="B5">
         <v>200101</v>
       </c>
       <c r="C5">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1355,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -1365,6 +1393,9 @@
       </c>
       <c r="Q5" t="b">
         <v>1</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/Tables/怪物表.xlsx
+++ b/Config/Excel/Tables/怪物表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28560" windowHeight="4650"/>
+    <workbookView windowWidth="25440" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,12 @@
     <t>Prefab</t>
   </si>
   <si>
+    <t>MoveAsset</t>
+  </si>
+  <si>
+    <t>JumpAsset</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -151,6 +157,12 @@
     <t>模型预制体</t>
   </si>
   <si>
+    <t>idle和移动动画资源</t>
+  </si>
+  <si>
+    <t>跳跃动画资源</t>
+  </si>
+  <si>
     <t>史莱姆</t>
   </si>
   <si>
@@ -163,6 +175,9 @@
     <t>Spitter</t>
   </si>
   <si>
+    <t>Jump</t>
+  </si>
+  <si>
     <t>史莱姆王</t>
   </si>
   <si>
@@ -170,6 +185,12 @@
   </si>
   <si>
     <t>201|202|203</t>
+  </si>
+  <si>
+    <t>MoveAsset1</t>
+  </si>
+  <si>
+    <t>Jump1</t>
   </si>
 </sst>
 </file>
@@ -804,7 +825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -813,6 +834,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1124,7 +1148,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="12" max="12" width="12.125" customWidth="1"/>
@@ -1132,9 +1156,11 @@
     <col min="14" max="14" width="18.25" customWidth="1"/>
     <col min="15" max="15" width="7.375" customWidth="1"/>
     <col min="17" max="17" width="11.125" customWidth="1"/>
+    <col min="19" max="19" width="19.5" customWidth="1"/>
+    <col min="20" max="20" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:18">
+    <row r="1" ht="14.25" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1187,118 +1213,136 @@
       <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="S1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" ht="14.25" spans="1:18">
+    <row r="2" ht="14.25" spans="1:20">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
-        <v>18</v>
-      </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O2" t="s">
-        <v>18</v>
-      </c>
-      <c r="P2" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>19</v>
+      <c r="S2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:18">
+    <row r="3" ht="14.25" spans="1:20">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="O3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="T3" t="s">
+        <v>43</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:18">
+    <row r="4" ht="14.25" spans="1:20">
       <c r="B4">
         <v>200001</v>
       </c>
@@ -1306,10 +1350,10 @@
         <v>1002</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4">
         <v>1</v>
@@ -1333,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -1345,10 +1389,16 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:18">
+    <row r="5" ht="14.25" spans="1:20">
       <c r="B5">
         <v>200101</v>
       </c>
@@ -1356,10 +1406,10 @@
         <v>1002</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -1383,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -1395,7 +1445,13 @@
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Excel/Tables/怪物表.xlsx
+++ b/Config/Excel/Tables/怪物表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="8700"/>
+    <workbookView windowWidth="26955" windowHeight="8610"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="52">
   <si>
     <t>##var</t>
   </si>
@@ -169,10 +169,10 @@
     <t>基础小怪</t>
   </si>
   <si>
-    <t>101|102</t>
-  </si>
-  <si>
-    <t>Spitter</t>
+    <t>Skeleton</t>
+  </si>
+  <si>
+    <t>SkeletonMove</t>
   </si>
   <si>
     <t>Jump</t>
@@ -182,12 +182,6 @@
   </si>
   <si>
     <t>示例boss</t>
-  </si>
-  <si>
-    <t>201|202|203</t>
-  </si>
-  <si>
-    <t>MoveAsset1</t>
   </si>
   <si>
     <t>Jump1</t>
@@ -1376,8 +1370,8 @@
       <c r="M4">
         <v>1</v>
       </c>
-      <c r="N4" t="s">
-        <v>46</v>
+      <c r="N4">
+        <v>5000</v>
       </c>
       <c r="O4">
         <v>1</v>
@@ -1389,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S4" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>17</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>48</v>
@@ -1432,8 +1426,8 @@
       <c r="M5">
         <v>1</v>
       </c>
-      <c r="N5" t="s">
-        <v>51</v>
+      <c r="N5">
+        <v>5000</v>
       </c>
       <c r="O5">
         <v>1000</v>
@@ -1445,13 +1439,13 @@
         <v>1</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="S5" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="T5" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
